--- a/Golden_State_Warriors_2025-26_stats.xlsx
+++ b/Golden_State_Warriors_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,60 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>21</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>49</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1231,7 +1285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2015,6 +2069,60 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2029,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2813,6 +2921,60 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2827,7 +2989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3611,6 +3773,60 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3647,7 +3863,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.1</v>
+        <v>29.09090909090909</v>
       </c>
     </row>
     <row r="3">
@@ -3657,7 +3873,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.08333333333333</v>
+        <v>19.23076923076923</v>
       </c>
     </row>
     <row r="4">
@@ -3677,7 +3893,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.27272727272727</v>
+        <v>11.58333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -3687,7 +3903,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.53846153846154</v>
+        <v>11.42857142857143</v>
       </c>
     </row>
     <row r="7">
@@ -3697,7 +3913,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.363636363636363</v>
+        <v>9.416666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -3707,7 +3923,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.75</v>
+        <v>7.615384615384615</v>
       </c>
     </row>
     <row r="9">
@@ -3717,27 +3933,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7.153846153846154</v>
+        <v>6.642857142857143</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Al Horford</t>
+          <t>Quinten Post</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5.642857142857143</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Quinten Post</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.846153846153846</v>
+        <v>5.333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3767,7 +3983,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.25</v>
+        <v>2.538461538461538</v>
       </c>
     </row>
     <row r="15">
@@ -3813,7 +4029,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.5</v>
+        <v>5.692307692307693</v>
       </c>
     </row>
     <row r="3">
@@ -3823,7 +4039,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.666666666666667</v>
+        <v>4.384615384615385</v>
       </c>
     </row>
     <row r="4">
@@ -3833,7 +4049,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9</v>
+        <v>3.727272727272727</v>
       </c>
     </row>
     <row r="5">
@@ -3843,7 +4059,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.153846153846154</v>
+        <v>3.142857142857143</v>
       </c>
     </row>
     <row r="6">
@@ -3873,7 +4089,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.636363636363636</v>
+        <v>1.583333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -3883,27 +4099,27 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.615384615384615</v>
+        <v>1.571428571428571</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Al Horford</t>
+          <t>Will Richard</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.5</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Will Richard</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.454545454545455</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -3923,7 +4139,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.083333333333333</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="14">
@@ -3933,7 +4149,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="15">
@@ -3989,7 +4205,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.333333333333333</v>
+        <v>5.538461538461538</v>
       </c>
     </row>
     <row r="4">
@@ -3999,7 +4215,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.25</v>
+        <v>5.461538461538462</v>
       </c>
     </row>
     <row r="5">
@@ -4009,7 +4225,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.769230769230769</v>
+        <v>4.642857142857143</v>
       </c>
     </row>
     <row r="6">
@@ -4019,7 +4235,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.25</v>
+        <v>4.111111111111111</v>
       </c>
     </row>
     <row r="7">
@@ -4029,7 +4245,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.769230769230769</v>
+        <v>3.642857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -4039,7 +4255,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5</v>
+        <v>3.545454545454545</v>
       </c>
     </row>
     <row r="9">
@@ -4049,7 +4265,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.636363636363636</v>
+        <v>2.666666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -4059,7 +4275,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.583333333333333</v>
+        <v>2.615384615384615</v>
       </c>
     </row>
     <row r="11">
@@ -4079,7 +4295,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.181818181818182</v>
+        <v>2.083333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -4095,21 +4311,21 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Buddy Hield</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.454545454545455</v>
+        <v>1.571428571428571</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Buddy Hield</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.384615384615385</v>
+        <v>1.454545454545455</v>
       </c>
     </row>
   </sheetData>
@@ -4145,7 +4361,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.1</v>
+        <v>4.545454545454546</v>
       </c>
     </row>
     <row r="3">
@@ -4155,7 +4371,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.818181818181818</v>
+        <v>2.583333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -4165,7 +4381,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.692307692307692</v>
+        <v>1.785714285714286</v>
       </c>
     </row>
     <row r="5">
@@ -4175,27 +4391,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.583333333333333</v>
+        <v>1.461538461538461</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Al Horford</t>
+          <t>Will Richard</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.5</v>
+        <v>1.416666666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Will Richard</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.363636363636364</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -4205,7 +4421,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.230769230769231</v>
+        <v>1.214285714285714</v>
       </c>
     </row>
     <row r="9">
@@ -4215,7 +4431,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.166666666666667</v>
+        <v>1.076923076923077</v>
       </c>
     </row>
     <row r="10">
@@ -4225,7 +4441,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.153846153846154</v>
+        <v>1.071428571428571</v>
       </c>
     </row>
     <row r="11">
@@ -4265,7 +4481,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.2307692307692308</v>
       </c>
     </row>
     <row r="15">
@@ -4289,7 +4505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4592,6 +4808,27 @@
         <v>245</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>109</v>
+      </c>
+      <c r="D15" t="n">
+        <v>108</v>
+      </c>
+      <c r="E15" t="n">
+        <v>217</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
